--- a/runs/KO/2026-10-13/bear/scratch/gen_wo_beta/dcf.xlsx
+++ b/runs/KO/2026-10-13/bear/scratch/gen_wo_beta/dcf.xlsx
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0.03</v>
@@ -1018,7 +1018,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>52862.02214222582</v>
+        <v>52363.32382012936</v>
       </c>
     </row>
     <row r="4">
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>17545.43376922617</v>
+        <v>17379.91080913914</v>
       </c>
     </row>
     <row r="6">
@@ -1240,7 +1240,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>13300.98841902524</v>
+        <v>13175.50739620425</v>
       </c>
     </row>
     <row r="12">
@@ -1351,7 +1351,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>9581.296912985519</v>
+        <v>9490.907319466791</v>
       </c>
     </row>
     <row r="16">
@@ -1419,7 +1419,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>52469.64424520014</v>
+        <v>51933.31123395747</v>
       </c>
     </row>
     <row r="21">
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>13092.49878734206</v>
+        <v>12968.98464783883</v>
       </c>
     </row>
     <row r="22">
@@ -1447,7 +1447,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>287008.6567651373</v>
+        <v>284301.0279277304</v>
       </c>
     </row>
     <row r="23">
@@ -1461,7 +1461,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>206745.173398584</v>
+        <v>204794.7472344464</v>
       </c>
     </row>
     <row r="24">
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>259214.8176437841</v>
+        <v>256728.0584684039</v>
       </c>
     </row>
     <row r="25">
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>279626.3176437841</v>
+        <v>277139.5584684039</v>
       </c>
     </row>
     <row r="27">
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>287299.2480702177</v>
+        <v>284662.1655217943</v>
       </c>
     </row>
     <row r="28">
@@ -1531,7 +1531,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>66.7827168921938</v>
+        <v>66.16972699251379</v>
       </c>
     </row>
     <row r="29">
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-0.2589578911</v>
+        <v>-0.2657598205</v>
       </c>
     </row>
   </sheetData>
